--- a/template.xlsx
+++ b/template.xlsx
@@ -1,43 +1,272 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\e-payslip\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334329DB-8377-4765-A6B3-F73E205F31F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{E324F944-70B3-4EFA-82D2-B56BF41E8252}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Kosong" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+  <si>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Arial Greek"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">HPCS SDN BHD 201201035336 (1019818-P)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <rFont val="Arial Greek"/>
+      </rPr>
+      <t>NO. 24-1, JALAN PULAU LUMUT Q U10/Q, TAMAN 
+ALAM  BUDIMAN SEKSYEN U10, 40170 SHAH ALAM, SELANGOR 
+Tel: +603 7842 3143 / +6019 3570 586
+Email: support@hpcs.my</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color indexed="10"/>
+        <rFont val="Arial Greek"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>PAYSLIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EARNINGS                                                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  RM               </t>
+  </si>
+  <si>
+    <t>DEDUCTIONS</t>
+  </si>
+  <si>
+    <t>RM</t>
+  </si>
+  <si>
+    <t>Basic Salary</t>
+  </si>
+  <si>
+    <t>EPF</t>
+  </si>
+  <si>
+    <t>Overtime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  -</t>
+  </si>
+  <si>
+    <t>SOCSO</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Employee's SOCSO Lindung 24 Jam</t>
+  </si>
+  <si>
+    <t>HPCS Staff Loan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Gross Pay                                                                       </t>
+  </si>
+  <si>
+    <t>Total Deductions</t>
+  </si>
+  <si>
+    <t>Net Pay</t>
+  </si>
+  <si>
+    <t>EMPLOYER'S CONTRIBUTIONS</t>
+  </si>
+  <si>
+    <t>EIS</t>
+  </si>
+  <si>
+    <t>TOTAL EMPLOYER CONTRIBUTIONS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepared By :                                            </t>
+  </si>
+  <si>
+    <t>Approved By :                                                       Employee's Signature</t>
+  </si>
+  <si>
+    <t>Finance &amp; Admin Executive</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee Name    : </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Position         : </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">NRIC             : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment Date    : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Account No : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary Month    : </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="13">
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Arial Greek"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Arial Greek"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Arial Greek"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color indexed="10"/>
+      <name val="Arial Greek"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF131313"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +274,69 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -66,6 +352,499 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>78922</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>328385</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1361</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{498E9A44-F29D-4B48-AB67-FFBFE38D0B34}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4910002" y="288290"/>
+          <a:ext cx="1453423" cy="833211"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:blipFill dpi="0" rotWithShape="0">
+                <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+                <a:srcRect/>
+                <a:stretch>
+                  <a:fillRect/>
+                </a:stretch>
+              </a:blipFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525" cap="flat">
+              <a:solidFill>
+                <a:srgbClr val="3465AF"/>
+              </a:solidFill>
+              <a:round/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>18586</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>83634</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>734122</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>92927</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5009B611-7901-42E6-AA20-C12214B4F26F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="209086" y="1889574"/>
+          <a:ext cx="8343156" cy="9293"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>32606</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>105937</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>4728</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>115230</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D584338D-6C48-424C-B3B3-C84A209AC586}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="223106" y="3176797"/>
+          <a:ext cx="8338882" cy="9293"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>26021</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>91068</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>741557</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>100361</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="Straight Connector 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4174606B-63FE-4E2D-B6A9-99B532E8056F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="216521" y="3527688"/>
+          <a:ext cx="8343156" cy="9293"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>27879</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>65048</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>74341</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="Straight Connector 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E95E6B2-0D6C-46CE-8EAD-90751133134C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="218379" y="3852188"/>
+          <a:ext cx="8338882" cy="9293"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>102220</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>715536</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>111513</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Straight Connector 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40CB57CF-35DB-4677-9FF0-90DA2CA49656}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="190500" y="5352400"/>
+          <a:ext cx="8343156" cy="9293"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>18585</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>83634</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>734121</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>92927</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="Straight Connector 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6833AC39-C8C2-4B02-B943-46466F226D23}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="209085" y="4968054"/>
+          <a:ext cx="8343156" cy="9293"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>17576</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>111513</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>733112</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>120806</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="Straight Connector 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE2373DE-606B-49E5-A154-10D6FE2341A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="208076" y="2283213"/>
+          <a:ext cx="8343156" cy="9293"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>27878</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>83635</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>92928</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="Straight Connector 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E58D9C38-4CFB-4030-9569-093759ED3D0C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="218378" y="4236535"/>
+          <a:ext cx="8338882" cy="9293"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -114,9 +893,9 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -149,9 +928,9 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -330,10 +1109,293 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E78099A3-7492-49E7-9C6D-80094326ECD2}">
+  <dimension ref="B2:L33"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2"/>
+  <cols>
+    <col min="1" max="1" width="2.77734375" customWidth="1"/>
+    <col min="5" max="5" width="9.21875" customWidth="1"/>
+    <col min="7" max="7" width="23.33203125" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" customWidth="1"/>
+    <col min="12" max="12" width="10.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12" ht="75" customHeight="1">
+      <c r="B2" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="L2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="3.45" customHeight="1"/>
+    <row r="4" spans="2:12" ht="21" customHeight="1">
+      <c r="B4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="2:12" ht="14.4" customHeight="1">
+      <c r="B5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="2:12" ht="15.6" customHeight="1">
+      <c r="B6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+    </row>
+    <row r="7" spans="2:12" ht="14.4">
+      <c r="B7" s="2"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+    </row>
+    <row r="8" spans="2:12" ht="14.4">
+      <c r="B8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="L8" s="5"/>
+    </row>
+    <row r="9" spans="2:12" ht="14.4">
+      <c r="B9" s="2"/>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" spans="2:12" ht="14.4">
+      <c r="B10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="H10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K10" s="12"/>
+    </row>
+    <row r="11" spans="2:12" ht="14.4">
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K11" s="12"/>
+    </row>
+    <row r="12" spans="2:12" ht="14.4">
+      <c r="B12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12" s="12"/>
+    </row>
+    <row r="13" spans="2:12">
+      <c r="H13" t="s">
+        <v>13</v>
+      </c>
+      <c r="K13" s="12"/>
+    </row>
+    <row r="14" spans="2:12" ht="14.4">
+      <c r="B14" s="2"/>
+      <c r="K14" s="14"/>
+    </row>
+    <row r="15" spans="2:12" ht="14.4">
+      <c r="B15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="11">
+        <f>SUM(F10:F12)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" s="15">
+        <f>SUM(K10:K13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="14.4">
+      <c r="B16" s="2"/>
+      <c r="K16" s="14"/>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="H17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="16">
+        <f>F15-K15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="14.4">
+      <c r="B18" s="2"/>
+    </row>
+    <row r="19" spans="2:12" ht="14.4">
+      <c r="B19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+    </row>
+    <row r="20" spans="2:12" ht="14.4">
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21" spans="2:12" ht="14.4">
+      <c r="B21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="12"/>
+    </row>
+    <row r="22" spans="2:12" ht="14.4">
+      <c r="B22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="12"/>
+    </row>
+    <row r="23" spans="2:12" ht="14.4">
+      <c r="B23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="12"/>
+    </row>
+    <row r="24" spans="2:12" ht="14.4">
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25" spans="2:12" ht="14.4">
+      <c r="B25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="17">
+        <f>SUM(F21:F23)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+    </row>
+    <row r="26" spans="2:12" ht="14.4">
+      <c r="B26" s="2"/>
+    </row>
+    <row r="27" spans="2:12" ht="5.7" customHeight="1">
+      <c r="B27" s="2"/>
+    </row>
+    <row r="28" spans="2:12">
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" ht="14.4">
+      <c r="B32" s="18"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="21"/>
+      <c r="F33" s="22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H6:L6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/template.xlsx
+++ b/template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\e-payslip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334329DB-8377-4765-A6B3-F73E205F31F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087369FE-F46A-4340-9412-8DE222B030B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{E324F944-70B3-4EFA-82D2-B56BF41E8252}"/>
   </bookViews>
@@ -287,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -333,10 +333,15 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1122,69 +1127,69 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="75" customHeight="1">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
       <c r="L2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="3.45" customHeight="1"/>
     <row r="4" spans="2:12" ht="21" customHeight="1">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="2" t="s">
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="2:12" ht="14.4" customHeight="1">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="2" t="s">
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="2:12" ht="15.6" customHeight="1">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="24" t="s">
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="2:12" ht="14.4">
       <c r="B7" s="2"/>
@@ -1228,7 +1233,7 @@
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="11"/>
+      <c r="F10" s="16"/>
       <c r="H10" t="s">
         <v>7</v>
       </c>
@@ -1301,12 +1306,12 @@
       <c r="B18" s="2"/>
     </row>
     <row r="19" spans="2:12" ht="14.4">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
@@ -1340,12 +1345,12 @@
       <c r="B24" s="2"/>
     </row>
     <row r="25" spans="2:12" ht="14.4">
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
       <c r="F25" s="17">
         <f>SUM(F21:F23)</f>
         <v>0</v>
@@ -1390,9 +1395,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="9">
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B25:E25"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="H4:L4"/>
+    <mergeCell ref="H5:L5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
